--- a/SuppXLS/Scen_Base_KS_setup.xlsx
+++ b/SuppXLS/Scen_Base_KS_setup.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook" updateLinks="never"/>
   <bookViews>
-    <workbookView windowHeight="7510" activeTab="8"/>
+    <workbookView windowWidth="18350" windowHeight="8710"/>
   </bookViews>
   <sheets>
     <sheet name="temp elec alignment" sheetId="17" r:id="rId1"/>
@@ -3428,9 +3428,10 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
+      <name val="Times New Roman"/>
+      <charset val="0"/>
     </font>
     <font>
       <b/>
@@ -3439,9 +3440,19 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="Tahoma"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="8"/>
       <name val="Tahoma"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
     </font>
     <font>
       <b/>
@@ -3456,17 +3467,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="Times New Roman"/>
-      <charset val="0"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="Tahoma"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
       <sz val="9"/>
       <name val="Times New Roman"/>
       <charset val="0"/>
@@ -11768,8 +11768,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="4:4">
-      <c r="D3" t="s">
+    <row r="2" spans="4:4">
+      <c r="D2" t="s">
         <v>2</v>
       </c>
     </row>
@@ -25157,7 +25157,7 @@
     <col min="5" max="5" width="8" customWidth="1"/>
     <col min="6" max="6" width="5" customWidth="1"/>
     <col min="7" max="7" width="2" customWidth="1"/>
-    <col min="9" max="9" width="19.7272727272727" customWidth="1"/>
+    <col min="9" max="9" width="67.8181818181818" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:2">

--- a/SuppXLS/Scen_Base_KS_setup.xlsx
+++ b/SuppXLS/Scen_Base_KS_setup.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\KiNESYS_BattCircularity-main\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE0AA607-4ADD-4E87-AE3C-C25C3F7DDC6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{645172BC-882C-45F6-87A5-435D67BFC62C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="3" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="temp elec alignment" sheetId="17" r:id="rId1"/>
@@ -743,7 +743,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3205" uniqueCount="711">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3207" uniqueCount="711">
   <si>
     <t>*this is to align the power sector with reality while we work with a reduced structure to explore batteries</t>
   </si>
@@ -2511,9 +2511,6 @@
     <t>Anthractie</t>
   </si>
   <si>
-    <t>ELCCO2Net</t>
-  </si>
-  <si>
     <t>NetCO2_ELC</t>
   </si>
   <si>
@@ -2878,6 +2875,9 @@
   </si>
   <si>
     <t>elchyd</t>
+  </si>
+  <si>
+    <t>ELCCO2N*,-*b</t>
   </si>
 </sst>
 </file>
@@ -2889,28 +2889,28 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="168" formatCode="0.0%"/>
-    <numFmt numFmtId="169" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="170" formatCode="m\o\n\th\ d\,\ yyyy"/>
-    <numFmt numFmtId="171" formatCode="_([$€]* #,##0.00_);_([$€]* \(#,##0.00\);_([$€]* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="172" formatCode="_([$€-2]* #,##0.00_);_([$€-2]* \(#,##0.00\);_([$€-2]* &quot;-&quot;??_)"/>
-    <numFmt numFmtId="173" formatCode="_-[$€-2]\ * #,##0.00_-;\-[$€-2]\ * #,##0.00_-;_-[$€-2]\ * &quot;-&quot;??_-"/>
-    <numFmt numFmtId="174" formatCode="_-[$€]* #,##0.00_-;\-[$€]* #,##0.00_-;_-[$€]* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="175" formatCode="_-&quot;€&quot;\ * #,##0.00_-;\-&quot;€&quot;\ * #,##0.00_-;_-&quot;€&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="176" formatCode="#.00"/>
-    <numFmt numFmtId="177" formatCode="#."/>
-    <numFmt numFmtId="178" formatCode="_-* #,##0.00\ _€_-;\-* #,##0.00\ _€_-;_-* &quot;-&quot;??\ _€_-;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="&quot;$&quot;#,##0_);\(&quot;$&quot;#,##0\)"/>
-    <numFmt numFmtId="180" formatCode="General_)"/>
-    <numFmt numFmtId="181" formatCode="\(##\);\(##\)"/>
-    <numFmt numFmtId="182" formatCode="#,##0;\-\ #,##0;_-\ &quot;- &quot;"/>
-    <numFmt numFmtId="183" formatCode="_ &quot;kr&quot;\ * #,##0_ ;_ &quot;kr&quot;\ * \-#,##0_ ;_ &quot;kr&quot;\ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="184" formatCode="yyyy"/>
-    <numFmt numFmtId="185" formatCode="#,##0.0"/>
-    <numFmt numFmtId="186" formatCode="_ &quot;kr&quot;\ * #,##0.00_ ;_ &quot;kr&quot;\ * \-#,##0.00_ ;_ &quot;kr&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="187" formatCode="0.00_);[Red]\(0.00\)"/>
-    <numFmt numFmtId="188" formatCode="0.0000"/>
-    <numFmt numFmtId="189" formatCode="0.0"/>
+    <numFmt numFmtId="166" formatCode="0.0%"/>
+    <numFmt numFmtId="167" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="168" formatCode="m\o\n\th\ d\,\ yyyy"/>
+    <numFmt numFmtId="169" formatCode="_([$€]* #,##0.00_);_([$€]* \(#,##0.00\);_([$€]* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="170" formatCode="_([$€-2]* #,##0.00_);_([$€-2]* \(#,##0.00\);_([$€-2]* &quot;-&quot;??_)"/>
+    <numFmt numFmtId="171" formatCode="_-[$€-2]\ * #,##0.00_-;\-[$€-2]\ * #,##0.00_-;_-[$€-2]\ * &quot;-&quot;??_-"/>
+    <numFmt numFmtId="172" formatCode="_-[$€]* #,##0.00_-;\-[$€]* #,##0.00_-;_-[$€]* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="173" formatCode="_-&quot;€&quot;\ * #,##0.00_-;\-&quot;€&quot;\ * #,##0.00_-;_-&quot;€&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="174" formatCode="#.00"/>
+    <numFmt numFmtId="175" formatCode="#."/>
+    <numFmt numFmtId="176" formatCode="_-* #,##0.00\ _€_-;\-* #,##0.00\ _€_-;_-* &quot;-&quot;??\ _€_-;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="&quot;$&quot;#,##0_);\(&quot;$&quot;#,##0\)"/>
+    <numFmt numFmtId="178" formatCode="General_)"/>
+    <numFmt numFmtId="179" formatCode="\(##\);\(##\)"/>
+    <numFmt numFmtId="180" formatCode="#,##0;\-\ #,##0;_-\ &quot;- &quot;"/>
+    <numFmt numFmtId="181" formatCode="_ &quot;kr&quot;\ * #,##0_ ;_ &quot;kr&quot;\ * \-#,##0_ ;_ &quot;kr&quot;\ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="182" formatCode="yyyy"/>
+    <numFmt numFmtId="183" formatCode="#,##0.0"/>
+    <numFmt numFmtId="184" formatCode="_ &quot;kr&quot;\ * #,##0.00_ ;_ &quot;kr&quot;\ * \-#,##0.00_ ;_ &quot;kr&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="185" formatCode="0.00_);[Red]\(0.00\)"/>
+    <numFmt numFmtId="186" formatCode="0.0000"/>
+    <numFmt numFmtId="187" formatCode="0.0"/>
   </numFmts>
   <fonts count="72">
     <font>
@@ -4715,41 +4715,41 @@
     <xf numFmtId="165" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="165" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="165" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="165" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="165" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="165" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="165" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -4938,15 +4938,15 @@
     <xf numFmtId="165" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="165" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="165" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="9">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="170" fontId="27" fillId="0" borderId="0">
+    <xf numFmtId="168" fontId="27" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="170" fontId="27" fillId="0" borderId="0">
+    <xf numFmtId="168" fontId="27" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="3" fontId="28" fillId="0" borderId="8">
@@ -4958,25 +4958,25 @@
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="169" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="171" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="171" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="172" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="172" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="172" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="172" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="172" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="172" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="172" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="172" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="173" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="173" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="172" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="174" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="175" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="175" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -4988,10 +4988,10 @@
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="176" fontId="27" fillId="0" borderId="0">
+    <xf numFmtId="174" fontId="27" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="176" fontId="27" fillId="0" borderId="0">
+    <xf numFmtId="174" fontId="27" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="11" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -5058,16 +5058,16 @@
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="177" fontId="38" fillId="0" borderId="0">
+    <xf numFmtId="175" fontId="38" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="177" fontId="38" fillId="0" borderId="0">
+    <xf numFmtId="175" fontId="38" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="177" fontId="38" fillId="0" borderId="0">
+    <xf numFmtId="175" fontId="38" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="177" fontId="38" fillId="0" borderId="0">
+    <xf numFmtId="175" fontId="38" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -5103,7 +5103,7 @@
     <xf numFmtId="0" fontId="43" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="43" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="44" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="45" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="45" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -5181,7 +5181,7 @@
     <xf numFmtId="0" fontId="71" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="71" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="71" fillId="0" borderId="0"/>
-    <xf numFmtId="179" fontId="47" fillId="0" borderId="0">
+    <xf numFmtId="177" fontId="47" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="71" fillId="0" borderId="0"/>
@@ -5208,16 +5208,16 @@
     <xf numFmtId="0" fontId="71" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="71" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="71" fillId="0" borderId="0"/>
-    <xf numFmtId="179" fontId="47" fillId="0" borderId="0">
+    <xf numFmtId="177" fontId="47" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="47" fillId="0" borderId="0">
+    <xf numFmtId="177" fontId="47" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="47" fillId="0" borderId="0">
+    <xf numFmtId="177" fontId="47" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="47" fillId="0" borderId="0">
+    <xf numFmtId="177" fontId="47" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="71" fillId="0" borderId="0"/>
@@ -5262,13 +5262,13 @@
     <xf numFmtId="0" fontId="71" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="71" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="71" fillId="0" borderId="0"/>
-    <xf numFmtId="179" fontId="47" fillId="0" borderId="0">
+    <xf numFmtId="177" fontId="47" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="47" fillId="0" borderId="0">
+    <xf numFmtId="177" fontId="47" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="47" fillId="0" borderId="0">
+    <xf numFmtId="177" fontId="47" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
@@ -5316,16 +5316,16 @@
     <xf numFmtId="0" fontId="71" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="71" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="71" fillId="0" borderId="0"/>
-    <xf numFmtId="179" fontId="47" fillId="0" borderId="0">
+    <xf numFmtId="177" fontId="47" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="47" fillId="0" borderId="0">
+    <xf numFmtId="177" fontId="47" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="47" fillId="0" borderId="0">
+    <xf numFmtId="177" fontId="47" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="47" fillId="0" borderId="0">
+    <xf numFmtId="177" fontId="47" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="71" fillId="0" borderId="0"/>
@@ -5334,7 +5334,7 @@
     <xf numFmtId="0" fontId="71" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="71" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="71" fillId="0" borderId="0"/>
-    <xf numFmtId="168" fontId="47" fillId="0" borderId="0">
+    <xf numFmtId="166" fontId="47" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="71" fillId="0" borderId="0"/>
@@ -5413,7 +5413,7 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
-    <xf numFmtId="168" fontId="47" fillId="0" borderId="0">
+    <xf numFmtId="166" fontId="47" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
@@ -5751,7 +5751,7 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
-    <xf numFmtId="180" fontId="47" fillId="0" borderId="0">
+    <xf numFmtId="178" fontId="47" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
@@ -6627,11 +6627,11 @@
     <xf numFmtId="0" fontId="14" fillId="24" borderId="19" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="14" fillId="24" borderId="19" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="14" fillId="24" borderId="19" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="181" fontId="50" fillId="0" borderId="0">
+    <xf numFmtId="179" fontId="50" fillId="0" borderId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="182" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="182" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="180" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="180" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="51" fillId="40" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="51" fillId="41" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="51" fillId="41" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
@@ -7396,7 +7396,7 @@
     <xf numFmtId="9" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="52" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="52" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="52" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="181" fontId="52" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -7425,16 +7425,16 @@
     <xf numFmtId="0" fontId="54" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="184" fontId="14" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="182" fontId="14" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="184" fontId="14" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="182" fontId="14" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="184" fontId="14" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="182" fontId="14" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="184" fontId="14" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="182" fontId="14" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0">
@@ -7449,13 +7449,13 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="185" fontId="55" fillId="44" borderId="21">
+    <xf numFmtId="183" fontId="55" fillId="44" borderId="21">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="56" fillId="44" borderId="21">
+    <xf numFmtId="166" fontId="56" fillId="44" borderId="21">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="185" fontId="57" fillId="45" borderId="21">
+    <xf numFmtId="183" fontId="57" fillId="45" borderId="21">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="46" borderId="22" applyBorder="0">
@@ -7515,7 +7515,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="25" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="25" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="186" fontId="52" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="184" fontId="52" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="43" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="43" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="43" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -7549,7 +7549,7 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="8"/>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="7"/>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="187" fontId="6" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="185" fontId="6" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="4" fontId="5" fillId="8" borderId="0" xfId="7" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="6"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
@@ -7566,7 +7566,7 @@
     <xf numFmtId="9" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="188" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="186" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -7584,7 +7584,7 @@
     <xf numFmtId="0" fontId="15" fillId="17" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="189" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="187" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="10" fillId="13" borderId="0" xfId="5" applyFill="1"/>
     <xf numFmtId="0" fontId="12" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -11317,7 +11317,7 @@
     </row>
     <row r="3" spans="1:41">
       <c r="D3" s="18" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
     </row>
     <row r="4" spans="1:41">
@@ -15599,10 +15599,10 @@
         <v>494</v>
       </c>
       <c r="Y29" t="s">
+        <v>710</v>
+      </c>
+      <c r="Z29" t="s">
         <v>588</v>
-      </c>
-      <c r="Z29" t="s">
-        <v>589</v>
       </c>
       <c r="AA29">
         <v>1E-3</v>
@@ -15617,7 +15617,7 @@
         <v>OIL</v>
       </c>
       <c r="G30" s="13" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H30" s="16">
         <v>4931.3</v>
@@ -15656,16 +15656,25 @@
         <v>55.99</v>
       </c>
       <c r="X30" t="s">
-        <v>276</v>
+        <v>494</v>
+      </c>
+      <c r="Y30" t="s">
+        <v>590</v>
+      </c>
+      <c r="Z30" t="s">
+        <v>588</v>
+      </c>
+      <c r="AA30">
+        <v>-1E-3</v>
       </c>
       <c r="AG30" s="18" t="s">
         <v>494</v>
       </c>
       <c r="AH30" s="18" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="AI30" s="18" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="AJ30" s="18">
         <v>-1E-3</v>
@@ -15673,14 +15682,14 @@
     </row>
     <row r="31" spans="1:36">
       <c r="A31" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B31" t="str">
         <f t="shared" si="0"/>
         <v>OVC</v>
       </c>
       <c r="G31" s="13" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H31" s="16">
         <v>3715.9</v>
@@ -15724,14 +15733,14 @@
     </row>
     <row r="32" spans="1:36">
       <c r="A32" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B32" t="str">
         <f t="shared" si="0"/>
         <v>PTC</v>
       </c>
       <c r="G32" s="13" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="H32" s="16">
         <v>2791.6</v>
@@ -15773,10 +15782,10 @@
         <v>494</v>
       </c>
       <c r="Y32" t="s">
+        <v>595</v>
+      </c>
+      <c r="Z32" t="s">
         <v>596</v>
-      </c>
-      <c r="Z32" t="s">
-        <v>597</v>
       </c>
       <c r="AA32">
         <v>1E-3</v>
@@ -15784,14 +15793,14 @@
     </row>
     <row r="33" spans="1:30">
       <c r="A33" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B33" t="str">
         <f t="shared" si="0"/>
         <v>COA</v>
       </c>
       <c r="G33" s="13" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H33" s="16">
         <v>6239.68</v>
@@ -15833,10 +15842,10 @@
         <v>494</v>
       </c>
       <c r="Y33" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="Z33" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="AA33">
         <v>-1E-3</v>
@@ -15844,14 +15853,14 @@
     </row>
     <row r="34" spans="1:30">
       <c r="A34" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B34" t="str">
         <f t="shared" si="0"/>
         <v>HFO</v>
       </c>
       <c r="G34" s="13" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="H34" s="13"/>
       <c r="I34" s="13"/>
@@ -15881,21 +15890,21 @@
     </row>
     <row r="35" spans="1:30">
       <c r="A35" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B35" t="str">
         <f t="shared" si="0"/>
         <v>KER</v>
       </c>
       <c r="G35" s="13" t="s">
+        <v>603</v>
+      </c>
+      <c r="H35" s="13" t="s">
         <v>604</v>
-      </c>
-      <c r="H35" s="13" t="s">
-        <v>605</v>
       </c>
       <c r="I35" s="13"/>
       <c r="J35" s="13" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="K35" s="13"/>
       <c r="L35" s="13">
@@ -15926,10 +15935,10 @@
         <v>494</v>
       </c>
       <c r="Y35" t="s">
+        <v>605</v>
+      </c>
+      <c r="Z35" t="s">
         <v>606</v>
-      </c>
-      <c r="Z35" t="s">
-        <v>607</v>
       </c>
       <c r="AA35">
         <v>1E-3</v>
@@ -15937,14 +15946,14 @@
     </row>
     <row r="36" spans="1:30">
       <c r="A36" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B36" t="str">
         <f t="shared" si="0"/>
         <v>LPG</v>
       </c>
       <c r="G36" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="H36" s="16">
         <v>5771</v>
@@ -15983,13 +15992,13 @@
         <v>76.28</v>
       </c>
       <c r="X36" s="4" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="Y36" t="s">
         <v>570</v>
       </c>
       <c r="Z36" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="AA36">
         <v>1E-3</v>
@@ -16004,7 +16013,7 @@
         <v>NGA</v>
       </c>
       <c r="G37" s="13" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="H37" s="16">
         <v>6160</v>
@@ -16046,10 +16055,10 @@
         <v>494</v>
       </c>
       <c r="Y37" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="Z37" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="AA37">
         <v>-1E-3</v>
@@ -16057,26 +16066,26 @@
     </row>
     <row r="38" spans="1:30">
       <c r="A38" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B38" t="str">
         <f t="shared" si="0"/>
         <v>OIL</v>
       </c>
       <c r="G38" s="13" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="H38" s="13">
         <v>924</v>
       </c>
       <c r="I38" s="13" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="J38" s="13">
         <v>419.12</v>
       </c>
       <c r="K38" s="13" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="L38" s="13">
         <v>210</v>
@@ -16109,7 +16118,7 @@
         <v>569</v>
       </c>
       <c r="Z38" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="AA38">
         <v>-1E-3</v>
@@ -16117,14 +16126,14 @@
     </row>
     <row r="39" spans="1:30">
       <c r="A39" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B39" t="str">
         <f t="shared" si="0"/>
         <v>BFG</v>
       </c>
       <c r="G39" s="13" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="H39" s="13"/>
       <c r="I39" s="13"/>
@@ -16154,14 +16163,14 @@
     </row>
     <row r="40" spans="1:30">
       <c r="A40" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B40" t="str">
         <f t="shared" si="0"/>
         <v>BIO</v>
       </c>
       <c r="G40" s="13" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="H40" s="13"/>
       <c r="I40" s="13"/>
@@ -16189,10 +16198,10 @@
         <v>494</v>
       </c>
       <c r="Y40" t="s">
+        <v>619</v>
+      </c>
+      <c r="Z40" t="s">
         <v>620</v>
-      </c>
-      <c r="Z40" t="s">
-        <v>621</v>
       </c>
       <c r="AA40">
         <v>1E-3</v>
@@ -16200,14 +16209,14 @@
     </row>
     <row r="41" spans="1:30">
       <c r="A41" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B41" t="str">
         <f t="shared" si="0"/>
         <v>COA</v>
       </c>
       <c r="G41" s="13" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H41" s="13"/>
       <c r="I41" s="13"/>
@@ -16235,10 +16244,10 @@
         <v>494</v>
       </c>
       <c r="Y41" t="s">
+        <v>623</v>
+      </c>
+      <c r="Z41" t="s">
         <v>624</v>
-      </c>
-      <c r="Z41" t="s">
-        <v>625</v>
       </c>
       <c r="AA41">
         <v>1E-3</v>
@@ -16246,7 +16255,7 @@
     </row>
     <row r="42" spans="1:30">
       <c r="A42" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B42" t="str">
         <f t="shared" si="0"/>
@@ -16270,7 +16279,7 @@
     </row>
     <row r="43" spans="1:30">
       <c r="A43" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B43" t="str">
         <f t="shared" si="0"/>
@@ -16294,7 +16303,7 @@
     </row>
     <row r="44" spans="1:30">
       <c r="A44" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B44" t="str">
         <f t="shared" si="0"/>
@@ -16318,7 +16327,7 @@
     </row>
     <row r="45" spans="1:30">
       <c r="A45" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B45" t="str">
         <f t="shared" si="0"/>
@@ -16345,7 +16354,7 @@
     </row>
     <row r="46" spans="1:30">
       <c r="A46" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B46" t="str">
         <f t="shared" si="0"/>
@@ -16390,7 +16399,7 @@
     </row>
     <row r="47" spans="1:30">
       <c r="A47" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B47" t="str">
         <f t="shared" si="0"/>
@@ -16415,13 +16424,13 @@
         <v>530</v>
       </c>
       <c r="Y47" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Z47" t="s">
         <v>399</v>
       </c>
       <c r="AA47" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="AB47">
         <v>0.9</v>
@@ -16458,13 +16467,13 @@
         <v>530</v>
       </c>
       <c r="Y48" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="Z48" t="s">
         <v>403</v>
       </c>
       <c r="AA48" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="AB48">
         <v>0.8</v>
@@ -16501,13 +16510,13 @@
         <v>530</v>
       </c>
       <c r="Y49" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="Z49" t="s">
         <v>281</v>
       </c>
       <c r="AA49" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="AB49">
         <v>0.95</v>
@@ -16522,7 +16531,7 @@
     </row>
     <row r="50" spans="1:31">
       <c r="A50" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B50" t="str">
         <f t="shared" si="0"/>
@@ -16570,7 +16579,7 @@
     </row>
     <row r="52" spans="1:31">
       <c r="A52" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B52" t="str">
         <f t="shared" si="0"/>
@@ -16622,7 +16631,7 @@
         <v>75</v>
       </c>
       <c r="Y53" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="Z53" t="s">
         <v>90</v>
@@ -16645,7 +16654,7 @@
     </row>
     <row r="54" spans="1:31">
       <c r="A54" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B54" t="str">
         <f t="shared" si="0"/>
@@ -16673,7 +16682,7 @@
         <v>565</v>
       </c>
       <c r="Z54" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="AA54" t="s">
         <v>530</v>
@@ -16688,7 +16697,7 @@
         <v>0.95</v>
       </c>
       <c r="AE54" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="55" spans="1:31">
@@ -16714,7 +16723,7 @@
         <v>556</v>
       </c>
       <c r="Z55" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="AA55" t="s">
         <v>530</v>
@@ -16729,7 +16738,7 @@
         <v>0.95</v>
       </c>
       <c r="AE55" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
   </sheetData>
@@ -16773,27 +16782,27 @@
   <sheetData>
     <row r="1" spans="2:23">
       <c r="M1" t="s">
+        <v>639</v>
+      </c>
+      <c r="S1" s="6" t="s">
         <v>640</v>
-      </c>
-      <c r="S1" s="6" t="s">
-        <v>641</v>
       </c>
     </row>
     <row r="2" spans="2:23">
       <c r="B2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="H2" t="s">
         <v>242</v>
       </c>
       <c r="I2" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="J2" t="s">
         <v>276</v>
       </c>
       <c r="K2" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="M2" t="s">
         <v>251</v>
@@ -16828,7 +16837,7 @@
     </row>
     <row r="3" spans="2:23">
       <c r="B3" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="C3" t="s">
         <v>310</v>
@@ -16843,7 +16852,7 @@
         <v>2019</v>
       </c>
       <c r="I3" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="K3" s="7">
         <v>803570.01532614301</v>
@@ -16880,7 +16889,7 @@
         <v>3</v>
       </c>
       <c r="W3" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="4" spans="2:23">
@@ -16894,7 +16903,7 @@
         <v>0.08</v>
       </c>
       <c r="E4" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H4">
         <v>2019</v>
@@ -16937,7 +16946,7 @@
         <v>3</v>
       </c>
       <c r="W4" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="5" spans="2:23">
@@ -16951,7 +16960,7 @@
         <v>0.01</v>
       </c>
       <c r="E5" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H5">
         <v>2019</v>
@@ -16994,7 +17003,7 @@
         <v>3</v>
       </c>
       <c r="W5" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="6" spans="2:23">
@@ -17008,7 +17017,7 @@
         <v>0.05</v>
       </c>
       <c r="E6" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H6">
         <v>2019</v>
@@ -17051,7 +17060,7 @@
         <v>3</v>
       </c>
       <c r="W6" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="7" spans="2:23">
@@ -17065,7 +17074,7 @@
         <v>3.7499999999999999E-2</v>
       </c>
       <c r="E7" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H7">
         <v>2019</v>
@@ -17108,7 +17117,7 @@
         <v>3</v>
       </c>
       <c r="W7" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="8" spans="2:23">
@@ -17122,7 +17131,7 @@
         <v>3.7499999999999999E-2</v>
       </c>
       <c r="E8" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H8">
         <v>2019</v>
@@ -17165,7 +17174,7 @@
         <v>3</v>
       </c>
       <c r="W8" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="9" spans="2:23">
@@ -17179,13 +17188,13 @@
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="E9" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H9">
         <v>2019</v>
       </c>
       <c r="I9" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="K9" s="7">
         <v>2160279.9224853502</v>
@@ -17222,7 +17231,7 @@
         <v>3</v>
       </c>
       <c r="W9" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="10" spans="2:23">
@@ -17236,13 +17245,13 @@
         <v>3.7499999999999999E-2</v>
       </c>
       <c r="E10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H10">
         <v>2019</v>
       </c>
       <c r="I10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="K10" s="7">
         <v>2096160.0225772699</v>
@@ -17279,7 +17288,7 @@
         <v>3</v>
       </c>
       <c r="W10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="11" spans="2:23">
@@ -17293,7 +17302,7 @@
         <v>0.08</v>
       </c>
       <c r="E11" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H11">
         <v>2019</v>
@@ -17336,7 +17345,7 @@
         <v>3</v>
       </c>
       <c r="W11" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="12" spans="2:23">
@@ -17350,7 +17359,7 @@
         <v>0.01</v>
       </c>
       <c r="E12" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H12">
         <v>2019</v>
@@ -17393,7 +17402,7 @@
         <v>3</v>
       </c>
       <c r="W12" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="13" spans="2:23">
@@ -17407,7 +17416,7 @@
         <v>3.7499999999999999E-2</v>
       </c>
       <c r="E13" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H13">
         <v>2019</v>
@@ -17450,7 +17459,7 @@
         <v>3</v>
       </c>
       <c r="W13" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="14" spans="2:23">
@@ -17464,7 +17473,7 @@
         <v>3.7499999999999999E-2</v>
       </c>
       <c r="E14" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H14">
         <v>2019</v>
@@ -17507,7 +17516,7 @@
         <v>3</v>
       </c>
       <c r="W14" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="15" spans="2:23">
@@ -17521,7 +17530,7 @@
         <v>0.08</v>
       </c>
       <c r="E15" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H15">
         <v>2019</v>
@@ -17564,7 +17573,7 @@
         <v>3</v>
       </c>
       <c r="W15" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="16" spans="2:23">
@@ -17578,7 +17587,7 @@
         <v>0.05</v>
       </c>
       <c r="E16" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H16">
         <v>2019</v>
@@ -17621,7 +17630,7 @@
         <v>3</v>
       </c>
       <c r="W16" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="17" spans="2:23">
@@ -17635,7 +17644,7 @@
         <v>0.08</v>
       </c>
       <c r="E17" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H17">
         <v>2019</v>
@@ -17678,7 +17687,7 @@
         <v>3</v>
       </c>
       <c r="W17" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="18" spans="2:23">
@@ -17692,7 +17701,7 @@
         <v>3.7499999999999999E-2</v>
       </c>
       <c r="E18" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H18">
         <v>2019</v>
@@ -17735,7 +17744,7 @@
         <v>3</v>
       </c>
       <c r="W18" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="19" spans="2:23">
@@ -17749,7 +17758,7 @@
         <v>0.1</v>
       </c>
       <c r="E19" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H19">
         <v>2019</v>
@@ -17792,7 +17801,7 @@
         <v>3</v>
       </c>
       <c r="W19" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="20" spans="2:23">
@@ -17806,7 +17815,7 @@
         <v>0.08</v>
       </c>
       <c r="E20" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H20">
         <v>2019</v>
@@ -17849,7 +17858,7 @@
         <v>3</v>
       </c>
       <c r="W20" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="21" spans="2:23">
@@ -17863,7 +17872,7 @@
         <v>0.08</v>
       </c>
       <c r="E21" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H21">
         <v>2019</v>
@@ -17906,7 +17915,7 @@
         <v>3</v>
       </c>
       <c r="W21" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="22" spans="2:23">
@@ -17920,7 +17929,7 @@
         <v>0.08</v>
       </c>
       <c r="E22" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H22">
         <v>2019</v>
@@ -17963,7 +17972,7 @@
         <v>3</v>
       </c>
       <c r="W22" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="23" spans="2:23">
@@ -17977,13 +17986,13 @@
         <v>0.08</v>
       </c>
       <c r="E23" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H23">
         <v>2019</v>
       </c>
       <c r="I23" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="K23" s="7">
         <v>268789.99939560902</v>
@@ -18020,7 +18029,7 @@
         <v>3</v>
       </c>
       <c r="W23" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="24" spans="2:23">
@@ -18034,7 +18043,7 @@
         <v>0.1</v>
       </c>
       <c r="E24" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H24">
         <v>2019</v>
@@ -18077,7 +18086,7 @@
         <v>3</v>
       </c>
       <c r="W24" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="25" spans="2:23" s="5" customFormat="1">
@@ -18091,7 +18100,7 @@
         <v>0.08</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H25" s="5">
         <v>2019</v>
@@ -18134,7 +18143,7 @@
         <v>3</v>
       </c>
       <c r="W25" s="5" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="26" spans="2:23">
@@ -18148,13 +18157,13 @@
         <v>0.08</v>
       </c>
       <c r="E26" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H26">
         <v>2019</v>
       </c>
       <c r="I26" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="K26" s="7">
         <v>10707219.7265625</v>
@@ -18191,7 +18200,7 @@
         <v>3</v>
       </c>
       <c r="W26" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="27" spans="2:23">
@@ -18205,7 +18214,7 @@
         <v>0.08</v>
       </c>
       <c r="E27" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H27">
         <v>2019</v>
@@ -18248,7 +18257,7 @@
         <v>3</v>
       </c>
       <c r="W27" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="28" spans="2:23">
@@ -18262,7 +18271,7 @@
         <v>0.1</v>
       </c>
       <c r="E28" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H28">
         <v>2019</v>
@@ -18305,7 +18314,7 @@
         <v>3</v>
       </c>
       <c r="W28" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="29" spans="2:23">
@@ -18319,7 +18328,7 @@
         <v>3.7499999999999999E-2</v>
       </c>
       <c r="E29" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H29">
         <v>2019</v>
@@ -18362,7 +18371,7 @@
         <v>3</v>
       </c>
       <c r="W29" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="30" spans="2:23">
@@ -18376,7 +18385,7 @@
         <v>0.01</v>
       </c>
       <c r="E30" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H30">
         <v>2019</v>
@@ -18419,7 +18428,7 @@
         <v>3</v>
       </c>
       <c r="W30" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="31" spans="2:23">
@@ -18433,7 +18442,7 @@
         <v>0.05</v>
       </c>
       <c r="E31" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H31">
         <v>2019</v>
@@ -18476,7 +18485,7 @@
         <v>3</v>
       </c>
       <c r="W31" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="32" spans="2:23">
@@ -18490,7 +18499,7 @@
         <v>0.08</v>
       </c>
       <c r="E32" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H32">
         <v>2019</v>
@@ -18533,7 +18542,7 @@
         <v>3</v>
       </c>
       <c r="W32" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="33" spans="2:23">
@@ -18547,7 +18556,7 @@
         <v>0.01</v>
       </c>
       <c r="E33" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H33">
         <v>2019</v>
@@ -18590,7 +18599,7 @@
         <v>3</v>
       </c>
       <c r="W33" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="34" spans="2:23">
@@ -18604,13 +18613,13 @@
         <v>0.08</v>
       </c>
       <c r="E34" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H34">
         <v>2019</v>
       </c>
       <c r="I34" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="K34" s="7">
         <v>384459.99336242699</v>
@@ -18647,7 +18656,7 @@
         <v>3</v>
       </c>
       <c r="W34" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="35" spans="2:23">
@@ -18661,7 +18670,7 @@
         <v>0.08</v>
       </c>
       <c r="E35" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H35">
         <v>2019</v>
@@ -18704,7 +18713,7 @@
         <v>3</v>
       </c>
       <c r="W35" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="36" spans="2:23">
@@ -18718,7 +18727,7 @@
         <v>0.05</v>
       </c>
       <c r="E36" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H36">
         <v>2019</v>
@@ -18761,7 +18770,7 @@
         <v>3</v>
       </c>
       <c r="W36" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="37" spans="2:23">
@@ -18775,7 +18784,7 @@
         <v>3.7499999999999999E-2</v>
       </c>
       <c r="E37" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H37">
         <v>2019</v>
@@ -18818,7 +18827,7 @@
         <v>3</v>
       </c>
       <c r="W37" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="38" spans="2:23">
@@ -18832,7 +18841,7 @@
         <v>0.05</v>
       </c>
       <c r="E38" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H38">
         <v>2019</v>
@@ -18875,7 +18884,7 @@
         <v>3</v>
       </c>
       <c r="W38" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="39" spans="2:23">
@@ -18889,13 +18898,13 @@
         <v>0.01</v>
       </c>
       <c r="E39" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H39">
         <v>2019</v>
       </c>
       <c r="I39" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="K39" s="7">
         <v>549359.98725891195</v>
@@ -18932,7 +18941,7 @@
         <v>3</v>
       </c>
       <c r="W39" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="40" spans="2:23">
@@ -18946,13 +18955,13 @@
         <v>3.7499999999999999E-2</v>
       </c>
       <c r="E40" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H40">
         <v>2019</v>
       </c>
       <c r="I40" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="K40" s="7">
         <v>1017650.03013611</v>
@@ -18989,7 +18998,7 @@
         <v>3</v>
       </c>
       <c r="W40" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="41" spans="2:23">
@@ -19003,7 +19012,7 @@
         <v>0.08</v>
       </c>
       <c r="E41" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H41">
         <v>2019</v>
@@ -19046,7 +19055,7 @@
         <v>3</v>
       </c>
       <c r="W41" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="42" spans="2:23">
@@ -19060,7 +19069,7 @@
         <v>0.05</v>
       </c>
       <c r="E42" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H42">
         <v>2019</v>
@@ -19103,7 +19112,7 @@
         <v>3</v>
       </c>
       <c r="W42" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="43" spans="2:23">
@@ -19117,13 +19126,13 @@
         <v>0.08</v>
       </c>
       <c r="E43" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H43">
         <v>2019</v>
       </c>
       <c r="I43" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="K43" s="7">
         <v>687100.02517700195</v>
@@ -19160,7 +19169,7 @@
         <v>3</v>
       </c>
       <c r="W43" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="44" spans="2:23">
@@ -19174,7 +19183,7 @@
         <v>0.01</v>
       </c>
       <c r="E44" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H44">
         <v>2019</v>
@@ -19217,7 +19226,7 @@
         <v>3</v>
       </c>
       <c r="W44" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="45" spans="2:23">
@@ -19231,13 +19240,13 @@
         <v>0.08</v>
       </c>
       <c r="E45" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H45">
         <v>2019</v>
       </c>
       <c r="I45" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K45" s="7">
         <v>348920.01342773403</v>
@@ -19274,7 +19283,7 @@
         <v>3</v>
       </c>
       <c r="W45" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="46" spans="2:23">
@@ -19288,7 +19297,7 @@
         <v>0.08</v>
       </c>
       <c r="E46" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H46">
         <v>2019</v>
@@ -19331,7 +19340,7 @@
         <v>3</v>
       </c>
       <c r="W46" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="47" spans="2:23">
@@ -19345,7 +19354,7 @@
         <v>0.08</v>
       </c>
       <c r="E47" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H47">
         <v>2019</v>
@@ -19388,7 +19397,7 @@
         <v>3</v>
       </c>
       <c r="W47" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="48" spans="2:23">
@@ -19402,13 +19411,13 @@
         <v>0.1</v>
       </c>
       <c r="E48" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H48">
         <v>2019</v>
       </c>
       <c r="I48" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="K48" s="7">
         <v>285119.99511718698</v>
@@ -19445,7 +19454,7 @@
         <v>3</v>
       </c>
       <c r="W48" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="49" spans="2:23">
@@ -19459,7 +19468,7 @@
         <v>0.08</v>
       </c>
       <c r="E49" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H49">
         <v>2019</v>
@@ -19502,7 +19511,7 @@
         <v>3</v>
       </c>
       <c r="W49" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="50" spans="2:23">
@@ -19516,7 +19525,7 @@
         <v>0.05</v>
       </c>
       <c r="E50" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H50">
         <v>2019</v>
@@ -19559,7 +19568,7 @@
         <v>3</v>
       </c>
       <c r="W50" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="51" spans="2:23">
@@ -19573,13 +19582,13 @@
         <v>0.05</v>
       </c>
       <c r="E51" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H51">
         <v>2019</v>
       </c>
       <c r="I51" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="K51" s="7">
         <v>2456300.0488281301</v>
@@ -19616,7 +19625,7 @@
         <v>3</v>
       </c>
       <c r="W51" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="52" spans="2:23">
@@ -19630,7 +19639,7 @@
         <v>0.08</v>
       </c>
       <c r="E52" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H52">
         <v>2019</v>
@@ -19673,7 +19682,7 @@
         <v>3</v>
       </c>
       <c r="W52" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="53" spans="2:23">
@@ -19687,13 +19696,13 @@
         <v>0.08</v>
       </c>
       <c r="E53" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H53">
         <v>2019</v>
       </c>
       <c r="I53" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="K53" s="7">
         <v>2178239.9616241399</v>
@@ -19730,7 +19739,7 @@
         <v>3</v>
       </c>
       <c r="W53" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="54" spans="2:23">
@@ -19744,7 +19753,7 @@
         <v>3.7499999999999999E-2</v>
       </c>
       <c r="E54" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H54">
         <v>2019</v>
@@ -19787,7 +19796,7 @@
         <v>3</v>
       </c>
       <c r="W54" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="55" spans="2:23">
@@ -19801,13 +19810,13 @@
         <v>3.7499999999999999E-2</v>
       </c>
       <c r="E55" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H55">
         <v>2019</v>
       </c>
       <c r="I55" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="K55" s="7">
         <v>883610.01014709496</v>
@@ -19844,7 +19853,7 @@
         <v>3</v>
       </c>
       <c r="W55" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="56" spans="2:23">
@@ -19858,7 +19867,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
       <c r="E56" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H56">
         <v>2019</v>
@@ -19901,7 +19910,7 @@
         <v>3</v>
       </c>
       <c r="W56" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="57" spans="2:23">
@@ -19915,7 +19924,7 @@
         <v>0.08</v>
       </c>
       <c r="E57" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H57">
         <v>2019</v>
@@ -19958,7 +19967,7 @@
         <v>3</v>
       </c>
       <c r="W57" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="58" spans="2:23">
@@ -19972,13 +19981,13 @@
         <v>0.05</v>
       </c>
       <c r="E58" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H58">
         <v>2019</v>
       </c>
       <c r="I58" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="K58" s="7">
         <v>35750</v>
@@ -20015,7 +20024,7 @@
         <v>3</v>
       </c>
       <c r="W58" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="59" spans="2:23">
@@ -20029,7 +20038,7 @@
         <v>3.7499999999999999E-2</v>
       </c>
       <c r="E59" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H59">
         <v>2019</v>
@@ -20072,7 +20081,7 @@
         <v>3</v>
       </c>
       <c r="W59" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="60" spans="2:23">
@@ -20086,7 +20095,7 @@
         <v>0.08</v>
       </c>
       <c r="E60" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H60">
         <v>2019</v>
@@ -20129,7 +20138,7 @@
         <v>3</v>
       </c>
       <c r="W60" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="61" spans="2:23">
@@ -20143,13 +20152,13 @@
         <v>0.08</v>
       </c>
       <c r="E61" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H61">
         <v>2019</v>
       </c>
       <c r="I61" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="K61" s="7">
         <v>318899.99020099599</v>
@@ -20186,7 +20195,7 @@
         <v>3</v>
       </c>
       <c r="W61" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="62" spans="2:23">
@@ -20200,7 +20209,7 @@
         <v>0.08</v>
       </c>
       <c r="E62" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H62">
         <v>2019</v>
@@ -20243,7 +20252,7 @@
         <v>3</v>
       </c>
       <c r="W62" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="63" spans="2:23">
@@ -20257,7 +20266,7 @@
         <v>0.08</v>
       </c>
       <c r="E63" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H63">
         <v>2019</v>
@@ -20300,7 +20309,7 @@
         <v>3</v>
       </c>
       <c r="W63" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="64" spans="2:23">
@@ -20314,7 +20323,7 @@
         <v>3.7499999999999999E-2</v>
       </c>
       <c r="E64" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H64">
         <v>2019</v>
@@ -20357,7 +20366,7 @@
         <v>3</v>
       </c>
       <c r="W64" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="65" spans="2:23">
@@ -20371,7 +20380,7 @@
         <v>0.01</v>
       </c>
       <c r="E65" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H65">
         <v>2019</v>
@@ -20414,7 +20423,7 @@
         <v>3</v>
       </c>
       <c r="W65" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="66" spans="2:23">
@@ -20428,7 +20437,7 @@
         <v>3.7499999999999999E-2</v>
       </c>
       <c r="E66" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H66">
         <v>2019</v>
@@ -20471,7 +20480,7 @@
         <v>3</v>
       </c>
       <c r="W66" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="67" spans="2:23">
@@ -20485,7 +20494,7 @@
         <v>0.08</v>
       </c>
       <c r="E67" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H67">
         <v>2019</v>
@@ -20528,7 +20537,7 @@
         <v>3</v>
       </c>
       <c r="W67" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="68" spans="2:23">
@@ -20542,7 +20551,7 @@
         <v>3.7499999999999999E-2</v>
       </c>
       <c r="E68" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H68">
         <v>2019</v>
@@ -20585,7 +20594,7 @@
         <v>3</v>
       </c>
       <c r="W68" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="69" spans="2:23">
@@ -20599,7 +20608,7 @@
         <v>0.1</v>
       </c>
       <c r="E69" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H69">
         <v>2019</v>
@@ -20642,7 +20651,7 @@
         <v>3</v>
       </c>
       <c r="W69" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="70" spans="2:23">
@@ -20656,7 +20665,7 @@
         <v>0.08</v>
       </c>
       <c r="E70" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H70">
         <v>2019</v>
@@ -20699,7 +20708,7 @@
         <v>3</v>
       </c>
       <c r="W70" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="71" spans="2:23">
@@ -20713,7 +20722,7 @@
         <v>0.08</v>
       </c>
       <c r="E71" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H71">
         <v>2019</v>
@@ -20756,7 +20765,7 @@
         <v>3</v>
       </c>
       <c r="W71" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="72" spans="2:23">
@@ -20770,7 +20779,7 @@
         <v>0.01</v>
       </c>
       <c r="E72" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H72">
         <v>2019</v>
@@ -20813,7 +20822,7 @@
         <v>3</v>
       </c>
       <c r="W72" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="73" spans="2:23">
@@ -20827,7 +20836,7 @@
         <v>0.08</v>
       </c>
       <c r="E73" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H73">
         <v>2019</v>
@@ -20870,7 +20879,7 @@
         <v>3</v>
       </c>
       <c r="W73" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="74" spans="2:23">
@@ -20884,7 +20893,7 @@
         <v>0.01</v>
       </c>
       <c r="E74" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H74">
         <v>2019</v>
@@ -20927,7 +20936,7 @@
         <v>3</v>
       </c>
       <c r="W74" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="75" spans="2:23">
@@ -20941,7 +20950,7 @@
         <v>0.01</v>
       </c>
       <c r="E75" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H75">
         <v>2019</v>
@@ -20984,7 +20993,7 @@
         <v>3</v>
       </c>
       <c r="W75" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="76" spans="2:23">
@@ -20998,7 +21007,7 @@
         <v>0.05</v>
       </c>
       <c r="E76" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H76">
         <v>2019</v>
@@ -21041,7 +21050,7 @@
         <v>3</v>
       </c>
       <c r="W76" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="77" spans="2:23">
@@ -21055,7 +21064,7 @@
         <v>0.08</v>
       </c>
       <c r="E77" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H77">
         <v>2019</v>
@@ -21098,7 +21107,7 @@
         <v>3</v>
       </c>
       <c r="W77" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="78" spans="2:23">
@@ -21112,7 +21121,7 @@
         <v>0.08</v>
       </c>
       <c r="E78" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H78">
         <v>2019</v>
@@ -21155,7 +21164,7 @@
         <v>3</v>
       </c>
       <c r="W78" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="79" spans="2:23">
@@ -21169,13 +21178,13 @@
         <v>0.08</v>
       </c>
       <c r="E79" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H79">
         <v>2019</v>
       </c>
       <c r="I79" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="K79" s="7">
         <v>8859.9996566772497</v>
@@ -21212,7 +21221,7 @@
         <v>3</v>
       </c>
       <c r="W79" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="80" spans="2:23">
@@ -21226,7 +21235,7 @@
         <v>0.08</v>
       </c>
       <c r="E80" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H80">
         <v>2019</v>
@@ -21269,7 +21278,7 @@
         <v>3</v>
       </c>
       <c r="W80" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="81" spans="2:23">
@@ -21283,7 +21292,7 @@
         <v>0.08</v>
       </c>
       <c r="E81" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H81">
         <v>2019</v>
@@ -21326,7 +21335,7 @@
         <v>3</v>
       </c>
       <c r="W81" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="82" spans="2:23">
@@ -21340,7 +21349,7 @@
         <v>0.08</v>
       </c>
       <c r="E82" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H82">
         <v>2019</v>
@@ -21383,7 +21392,7 @@
         <v>3</v>
       </c>
       <c r="W82" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="83" spans="2:23">
@@ -21397,7 +21406,7 @@
         <v>3.7499999999999999E-2</v>
       </c>
       <c r="E83" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H83">
         <v>2019</v>
@@ -21440,7 +21449,7 @@
         <v>3</v>
       </c>
       <c r="W83" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="84" spans="2:23">
@@ -21454,7 +21463,7 @@
         <v>0.08</v>
       </c>
       <c r="E84" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H84">
         <v>2019</v>
@@ -21497,7 +21506,7 @@
         <v>3</v>
       </c>
       <c r="W84" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="85" spans="2:23">
@@ -21511,7 +21520,7 @@
         <v>0.08</v>
       </c>
       <c r="E85" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H85">
         <v>2019</v>
@@ -21554,7 +21563,7 @@
         <v>3</v>
       </c>
       <c r="W85" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="86" spans="2:23">
@@ -21568,7 +21577,7 @@
         <v>0.08</v>
       </c>
       <c r="E86" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H86">
         <v>2019</v>
@@ -21611,7 +21620,7 @@
         <v>3</v>
       </c>
       <c r="W86" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="87" spans="2:23">
@@ -21625,7 +21634,7 @@
         <v>0.08</v>
       </c>
       <c r="E87" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H87">
         <v>2019</v>
@@ -21668,7 +21677,7 @@
         <v>3</v>
       </c>
       <c r="W87" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="88" spans="2:23">
@@ -21682,7 +21691,7 @@
         <v>0.08</v>
       </c>
       <c r="E88" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H88">
         <v>2019</v>
@@ -21725,7 +21734,7 @@
         <v>3</v>
       </c>
       <c r="W88" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="89" spans="2:23">
@@ -21739,7 +21748,7 @@
         <v>0.08</v>
       </c>
       <c r="E89" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H89">
         <v>2019</v>
@@ -21782,7 +21791,7 @@
         <v>3</v>
       </c>
       <c r="W89" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="90" spans="2:23">
@@ -21796,13 +21805,13 @@
         <v>0.08</v>
       </c>
       <c r="E90" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H90">
         <v>2019</v>
       </c>
       <c r="I90" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="K90" s="7">
         <v>272640.00320434599</v>
@@ -21839,7 +21848,7 @@
         <v>3</v>
       </c>
       <c r="W90" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="91" spans="2:23">
@@ -21853,7 +21862,7 @@
         <v>0.08</v>
       </c>
       <c r="E91" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H91">
         <v>2019</v>
@@ -21896,7 +21905,7 @@
         <v>3</v>
       </c>
       <c r="W91" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="92" spans="2:23">
@@ -21910,13 +21919,13 @@
         <v>0.08</v>
       </c>
       <c r="E92" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H92">
         <v>2019</v>
       </c>
       <c r="I92" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="K92" s="7">
         <v>37590.000748634397</v>
@@ -21953,7 +21962,7 @@
         <v>3</v>
       </c>
       <c r="W92" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="93" spans="2:23">
@@ -21967,7 +21976,7 @@
         <v>0.08</v>
       </c>
       <c r="E93" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H93">
         <v>2019</v>
@@ -22010,7 +22019,7 @@
         <v>3</v>
       </c>
       <c r="W93" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="94" spans="2:23">
@@ -22024,7 +22033,7 @@
         <v>3.7499999999999999E-2</v>
       </c>
       <c r="E94" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H94">
         <v>2019</v>
@@ -22067,7 +22076,7 @@
         <v>3</v>
       </c>
       <c r="W94" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="95" spans="2:23">
@@ -22081,7 +22090,7 @@
         <v>0.04</v>
       </c>
       <c r="E95" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H95">
         <v>2019</v>
@@ -22124,7 +22133,7 @@
         <v>3</v>
       </c>
       <c r="W95" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="96" spans="2:23">
@@ -22138,7 +22147,7 @@
         <v>3.7499999999999999E-2</v>
       </c>
       <c r="E96" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H96">
         <v>2019</v>
@@ -22181,7 +22190,7 @@
         <v>3</v>
       </c>
       <c r="W96" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="97" spans="2:23">
@@ -22195,7 +22204,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
       <c r="E97" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H97">
         <v>2019</v>
@@ -22238,7 +22247,7 @@
         <v>3</v>
       </c>
       <c r="W97" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="98" spans="2:23">
@@ -22252,7 +22261,7 @@
         <v>0.08</v>
       </c>
       <c r="E98" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H98">
         <v>2019</v>
@@ -22295,7 +22304,7 @@
         <v>3</v>
       </c>
       <c r="W98" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="99" spans="2:23">
@@ -22309,7 +22318,7 @@
         <v>0.08</v>
       </c>
       <c r="E99" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H99">
         <v>2019</v>
@@ -22352,7 +22361,7 @@
         <v>3</v>
       </c>
       <c r="W99" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="100" spans="2:23">
@@ -22366,7 +22375,7 @@
         <v>3.7499999999999999E-2</v>
       </c>
       <c r="E100" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H100">
         <v>2019</v>
@@ -22409,7 +22418,7 @@
         <v>3</v>
       </c>
       <c r="W100" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="101" spans="2:23">
@@ -22423,7 +22432,7 @@
         <v>3.7499999999999999E-2</v>
       </c>
       <c r="E101" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H101">
         <v>2019</v>
@@ -22466,7 +22475,7 @@
         <v>3</v>
       </c>
       <c r="W101" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="102" spans="2:23">
@@ -22480,7 +22489,7 @@
         <v>0.08</v>
       </c>
       <c r="E102" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H102">
         <v>2019</v>
@@ -22523,7 +22532,7 @@
         <v>3</v>
       </c>
       <c r="W102" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="103" spans="2:23">
@@ -22537,13 +22546,13 @@
         <v>3.7499999999999999E-2</v>
       </c>
       <c r="E103" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H103">
         <v>2019</v>
       </c>
       <c r="I103" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="K103" s="7">
         <v>295130.00488281302</v>
@@ -22580,7 +22589,7 @@
         <v>3</v>
       </c>
       <c r="W103" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="104" spans="2:23">
@@ -22594,7 +22603,7 @@
         <v>0.05</v>
       </c>
       <c r="E104" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H104">
         <v>2019</v>
@@ -22637,7 +22646,7 @@
         <v>3</v>
       </c>
       <c r="W104" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="105" spans="2:23">
@@ -22651,7 +22660,7 @@
         <v>3.7499999999999999E-2</v>
       </c>
       <c r="E105" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H105">
         <v>2019</v>
@@ -22694,7 +22703,7 @@
         <v>3</v>
       </c>
       <c r="W105" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="106" spans="2:23">
@@ -22708,7 +22717,7 @@
         <v>0.08</v>
       </c>
       <c r="E106" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H106">
         <v>2019</v>
@@ -22751,7 +22760,7 @@
         <v>3</v>
       </c>
       <c r="W106" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="107" spans="2:23">
@@ -22765,7 +22774,7 @@
         <v>0.1</v>
       </c>
       <c r="E107" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H107">
         <v>2019</v>
@@ -22808,7 +22817,7 @@
         <v>3</v>
       </c>
       <c r="W107" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="108" spans="2:23">
@@ -22822,7 +22831,7 @@
         <v>3.7499999999999999E-2</v>
       </c>
       <c r="E108" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H108">
         <v>2019</v>
@@ -22865,7 +22874,7 @@
         <v>3</v>
       </c>
       <c r="W108" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="109" spans="2:23">
@@ -22879,7 +22888,7 @@
         <v>3.7499999999999999E-2</v>
       </c>
       <c r="E109" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H109">
         <v>2019</v>
@@ -22922,7 +22931,7 @@
         <v>3</v>
       </c>
       <c r="W109" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="110" spans="2:23">
@@ -22936,7 +22945,7 @@
         <v>0.08</v>
       </c>
       <c r="E110" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H110">
         <v>2019</v>
@@ -22979,7 +22988,7 @@
         <v>3</v>
       </c>
       <c r="W110" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="111" spans="2:23">
@@ -22993,7 +23002,7 @@
         <v>0.08</v>
       </c>
       <c r="E111" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H111">
         <v>2019</v>
@@ -23036,7 +23045,7 @@
         <v>3</v>
       </c>
       <c r="W111" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="112" spans="2:23">
@@ -23050,7 +23059,7 @@
         <v>3.7499999999999999E-2</v>
       </c>
       <c r="E112" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H112">
         <v>2019</v>
@@ -23093,7 +23102,7 @@
         <v>3</v>
       </c>
       <c r="W112" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="113" spans="2:23">
@@ -23141,12 +23150,12 @@
         <v>3</v>
       </c>
       <c r="W113" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="114" spans="2:23">
       <c r="B114" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="C114" t="s">
         <v>496</v>
@@ -23155,13 +23164,13 @@
         <v>3.7499999999999999E-2</v>
       </c>
       <c r="E114" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H114">
         <v>2019</v>
       </c>
       <c r="I114" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="K114">
         <v>242929.99792098999</v>
@@ -23198,12 +23207,12 @@
         <v>3</v>
       </c>
       <c r="W114" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="115" spans="2:23">
       <c r="B115" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="C115" t="s">
         <v>496</v>
@@ -23212,7 +23221,7 @@
         <v>3.7499999999999999E-2</v>
       </c>
       <c r="E115" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H115">
         <v>2019</v>
@@ -23255,12 +23264,12 @@
         <v>3</v>
       </c>
       <c r="W115" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="116" spans="2:23">
       <c r="B116" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="C116" t="s">
         <v>496</v>
@@ -23269,7 +23278,7 @@
         <v>3.7499999999999999E-2</v>
       </c>
       <c r="E116" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H116">
         <v>2019</v>
@@ -23312,12 +23321,12 @@
         <v>3</v>
       </c>
       <c r="W116" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="117" spans="2:23">
       <c r="B117" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="C117" t="s">
         <v>496</v>
@@ -23326,7 +23335,7 @@
         <v>0.08</v>
       </c>
       <c r="E117" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H117">
         <v>2019</v>
@@ -23369,12 +23378,12 @@
         <v>3</v>
       </c>
       <c r="W117" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="118" spans="2:23">
       <c r="B118" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="C118" t="s">
         <v>496</v>
@@ -23383,7 +23392,7 @@
         <v>0.08</v>
       </c>
       <c r="E118" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H118">
         <v>2019</v>
@@ -23426,12 +23435,12 @@
         <v>3</v>
       </c>
       <c r="W118" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="119" spans="2:23">
       <c r="B119" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="C119" t="s">
         <v>496</v>
@@ -23440,13 +23449,13 @@
         <v>0.08</v>
       </c>
       <c r="E119" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H119">
         <v>2019</v>
       </c>
       <c r="I119" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="K119">
         <v>75709.9990844727</v>
@@ -23483,12 +23492,12 @@
         <v>3</v>
       </c>
       <c r="W119" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="120" spans="2:23">
       <c r="B120" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="C120" t="s">
         <v>496</v>
@@ -23497,7 +23506,7 @@
         <v>0.08</v>
       </c>
       <c r="E120" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H120">
         <v>2019</v>
@@ -23540,12 +23549,12 @@
         <v>3</v>
       </c>
       <c r="W120" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="121" spans="2:23">
       <c r="B121" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="C121" t="s">
         <v>496</v>
@@ -23554,13 +23563,13 @@
         <v>0.08</v>
       </c>
       <c r="E121" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H121">
         <v>2019</v>
       </c>
       <c r="I121" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="K121">
         <v>37380.001068115198</v>
@@ -23597,12 +23606,12 @@
         <v>3</v>
       </c>
       <c r="W121" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="122" spans="2:23">
       <c r="B122" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="C122" t="s">
         <v>496</v>
@@ -23611,7 +23620,7 @@
         <v>0.08</v>
       </c>
       <c r="E122" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H122">
         <v>2019</v>
@@ -23654,7 +23663,7 @@
         <v>3</v>
       </c>
       <c r="W122" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="123" spans="2:23">
@@ -23668,7 +23677,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="E123" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H123">
         <v>2019</v>
@@ -23711,12 +23720,12 @@
         <v>3</v>
       </c>
       <c r="W123" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="124" spans="2:23">
       <c r="B124" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="C124" t="s">
         <v>496</v>
@@ -23725,7 +23734,7 @@
         <v>3.7499999999999999E-2</v>
       </c>
       <c r="E124" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H124">
         <v>2019</v>
@@ -23768,7 +23777,7 @@
         <v>3</v>
       </c>
       <c r="W124" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="125" spans="2:23">
@@ -23782,7 +23791,7 @@
         <v>0.08</v>
       </c>
       <c r="E125" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H125">
         <v>2019</v>
@@ -23825,7 +23834,7 @@
         <v>3</v>
       </c>
       <c r="W125" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="126" spans="2:23">
@@ -23839,7 +23848,7 @@
         <v>3.7499999999999999E-2</v>
       </c>
       <c r="E126" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H126">
         <v>2019</v>
@@ -23882,12 +23891,12 @@
         <v>3</v>
       </c>
       <c r="W126" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="127" spans="2:23">
       <c r="B127" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="C127" t="s">
         <v>496</v>
@@ -23896,13 +23905,13 @@
         <v>0.08</v>
       </c>
       <c r="E127" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H127">
         <v>2019</v>
       </c>
       <c r="I127" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="K127">
         <v>396839.99633789097</v>
@@ -23939,12 +23948,12 @@
         <v>3</v>
       </c>
       <c r="W127" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="128" spans="2:23">
       <c r="B128" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="C128" t="s">
         <v>496</v>
@@ -23953,7 +23962,7 @@
         <v>0.08</v>
       </c>
       <c r="E128" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H128">
         <v>2019</v>
@@ -23996,12 +24005,12 @@
         <v>3</v>
       </c>
       <c r="W128" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="129" spans="2:23">
       <c r="B129" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="C129" t="s">
         <v>496</v>
@@ -24010,7 +24019,7 @@
         <v>0.01</v>
       </c>
       <c r="E129" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H129">
         <v>2019</v>
@@ -24053,12 +24062,12 @@
         <v>3</v>
       </c>
       <c r="W129" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="130" spans="2:23">
       <c r="B130" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="C130" t="s">
         <v>496</v>
@@ -24067,7 +24076,7 @@
         <v>0.05</v>
       </c>
       <c r="E130" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H130">
         <v>2019</v>
@@ -24110,12 +24119,12 @@
         <v>3</v>
       </c>
       <c r="W130" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="131" spans="2:23">
       <c r="B131" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="C131" t="s">
         <v>496</v>
@@ -24124,7 +24133,7 @@
         <v>0.08</v>
       </c>
       <c r="E131" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H131">
         <v>2019</v>
@@ -24167,12 +24176,12 @@
         <v>3</v>
       </c>
       <c r="W131" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="132" spans="2:23">
       <c r="B132" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="C132" t="s">
         <v>496</v>
@@ -24181,13 +24190,13 @@
         <v>0.08</v>
       </c>
       <c r="E132" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H132">
         <v>2019</v>
       </c>
       <c r="I132" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="K132">
         <v>174729.995727539</v>
@@ -24224,12 +24233,12 @@
         <v>3</v>
       </c>
       <c r="W132" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="133" spans="2:23">
       <c r="B133" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="C133" t="s">
         <v>496</v>
@@ -24238,7 +24247,7 @@
         <v>0.08</v>
       </c>
       <c r="E133" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H133">
         <v>2019</v>
@@ -24281,12 +24290,12 @@
         <v>3</v>
       </c>
       <c r="W133" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="134" spans="2:23">
       <c r="B134" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="C134" t="s">
         <v>496</v>
@@ -24295,7 +24304,7 @@
         <v>0.08</v>
       </c>
       <c r="E134" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H134">
         <v>2019</v>
@@ -24338,12 +24347,12 @@
         <v>3</v>
       </c>
       <c r="W134" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="135" spans="2:23">
       <c r="B135" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C135" t="s">
         <v>496</v>
@@ -24352,7 +24361,7 @@
         <v>0.01</v>
       </c>
       <c r="E135" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H135">
         <v>2019</v>
@@ -24395,12 +24404,12 @@
         <v>3</v>
       </c>
       <c r="W135" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="136" spans="2:23">
       <c r="B136" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="C136" t="s">
         <v>496</v>
@@ -24409,7 +24418,7 @@
         <v>0.08</v>
       </c>
       <c r="E136" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H136">
         <v>2019</v>
@@ -24452,12 +24461,12 @@
         <v>3</v>
       </c>
       <c r="W136" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="137" spans="2:23">
       <c r="B137" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C137" t="s">
         <v>496</v>
@@ -24466,13 +24475,13 @@
         <v>0.08</v>
       </c>
       <c r="E137" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H137">
         <v>2019</v>
       </c>
       <c r="I137" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="K137">
         <v>82750.000476837202</v>
@@ -24509,12 +24518,12 @@
         <v>3</v>
       </c>
       <c r="W137" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="138" spans="2:23">
       <c r="B138" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C138" t="s">
         <v>496</v>
@@ -24523,7 +24532,7 @@
         <v>0.04</v>
       </c>
       <c r="E138" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H138">
         <v>2019</v>
@@ -24566,12 +24575,12 @@
         <v>3</v>
       </c>
       <c r="W138" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="139" spans="2:23">
       <c r="B139" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="C139" t="s">
         <v>496</v>
@@ -24580,7 +24589,7 @@
         <v>0.08</v>
       </c>
       <c r="E139" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H139">
         <v>2019</v>
@@ -24623,7 +24632,7 @@
         <v>3</v>
       </c>
       <c r="W139" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="140" spans="2:23">
@@ -24637,12 +24646,12 @@
         <v>0.08</v>
       </c>
       <c r="E140" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
     </row>
     <row r="141" spans="2:23">
       <c r="B141" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C141" t="s">
         <v>496</v>
@@ -24651,12 +24660,12 @@
         <v>0.05</v>
       </c>
       <c r="E141" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
     </row>
     <row r="142" spans="2:23">
       <c r="B142" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="C142" t="s">
         <v>496</v>
@@ -24665,12 +24674,12 @@
         <v>0.1</v>
       </c>
       <c r="E142" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
     </row>
     <row r="143" spans="2:23">
       <c r="B143" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="C143" t="s">
         <v>496</v>
@@ -24679,7 +24688,7 @@
         <v>0.08</v>
       </c>
       <c r="E143" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
     </row>
   </sheetData>
@@ -24711,7 +24720,7 @@
     </row>
     <row r="5" spans="2:9">
       <c r="C5" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="6" spans="2:9">
@@ -24742,7 +24751,7 @@
     </row>
     <row r="7" spans="2:9" s="1" customFormat="1">
       <c r="B7" s="1" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>280</v>
@@ -24761,10 +24770,10 @@
         <v>3</v>
       </c>
       <c r="H7" s="1" t="s">
+        <v>675</v>
+      </c>
+      <c r="I7" s="1" t="s">
         <v>676</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>677</v>
       </c>
     </row>
     <row r="8" spans="2:9">
@@ -24772,7 +24781,7 @@
         <v>111</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="E8" s="4">
         <v>-60</v>
@@ -24780,7 +24789,7 @@
       <c r="F8" s="4"/>
       <c r="G8" s="4"/>
       <c r="H8" s="4" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
     </row>
     <row r="9" spans="2:9">
@@ -24788,7 +24797,7 @@
         <v>111</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="E9" s="4">
         <v>-180</v>
@@ -24796,7 +24805,7 @@
       <c r="F9" s="4"/>
       <c r="G9" s="4"/>
       <c r="H9" s="4" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
     </row>
     <row r="10" spans="2:9">
@@ -24804,13 +24813,13 @@
         <v>111</v>
       </c>
       <c r="D10" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="E10">
         <v>-600</v>
       </c>
       <c r="H10" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
     </row>
     <row r="12" spans="2:9" s="2" customFormat="1"/>
@@ -24819,7 +24828,7 @@
     <row r="15" spans="2:9" s="2" customFormat="1"/>
     <row r="17" spans="2:9">
       <c r="C17" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
     </row>
     <row r="18" spans="2:9">
@@ -24850,13 +24859,13 @@
     </row>
     <row r="19" spans="2:9">
       <c r="B19" t="s">
+        <v>681</v>
+      </c>
+      <c r="C19" t="s">
         <v>682</v>
       </c>
-      <c r="C19" t="s">
-        <v>683</v>
-      </c>
       <c r="D19" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="E19">
         <v>1</v>
@@ -24868,7 +24877,7 @@
         <v>3</v>
       </c>
       <c r="I19" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
     </row>
     <row r="20" spans="2:9">
@@ -24876,13 +24885,13 @@
         <v>111</v>
       </c>
       <c r="D20" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="E20">
         <v>-60</v>
       </c>
       <c r="H20" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
     </row>
     <row r="21" spans="2:9">
@@ -24890,13 +24899,13 @@
         <v>111</v>
       </c>
       <c r="D21" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="E21">
         <v>-180</v>
       </c>
       <c r="H21" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
     </row>
     <row r="22" spans="2:9">
@@ -24904,7 +24913,7 @@
         <v>111</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="E22" s="2">
         <v>-600</v>
@@ -24912,7 +24921,7 @@
       <c r="F22" s="2"/>
       <c r="G22" s="2"/>
       <c r="H22" s="2" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
     </row>
     <row r="23" spans="2:9">
@@ -24920,7 +24929,7 @@
         <v>111</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="E23" s="2">
         <v>-14.7692307692308</v>
@@ -24928,7 +24937,7 @@
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
       <c r="H23" s="2" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
     </row>
     <row r="24" spans="2:9">
@@ -24936,7 +24945,7 @@
         <v>111</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="E24" s="2">
         <v>-16.842105263157901</v>
@@ -24944,7 +24953,7 @@
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
       <c r="H24" s="2" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
     </row>
     <row r="25" spans="2:9">
@@ -24952,13 +24961,13 @@
         <v>111</v>
       </c>
       <c r="D25" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="E25">
         <v>-600</v>
       </c>
       <c r="H25" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
     </row>
   </sheetData>
@@ -26886,10 +26895,10 @@
   <sheetData>
     <row r="3" spans="3:21">
       <c r="C3" s="51" t="s">
+        <v>688</v>
+      </c>
+      <c r="R3" s="51" t="s">
         <v>689</v>
-      </c>
-      <c r="R3" s="51" t="s">
-        <v>690</v>
       </c>
     </row>
     <row r="4" spans="3:21">
@@ -26906,37 +26915,37 @@
         <v>242</v>
       </c>
       <c r="G4" s="51" t="s">
+        <v>690</v>
+      </c>
+      <c r="H4" s="51" t="s">
         <v>691</v>
       </c>
-      <c r="H4" s="51" t="s">
+      <c r="I4" s="51" t="s">
         <v>692</v>
       </c>
-      <c r="I4" s="51" t="s">
+      <c r="J4" s="51" t="s">
         <v>693</v>
       </c>
-      <c r="J4" s="51" t="s">
+      <c r="K4" s="51" t="s">
         <v>694</v>
       </c>
-      <c r="K4" s="51" t="s">
+      <c r="L4" s="51" t="s">
         <v>695</v>
       </c>
-      <c r="L4" s="51" t="s">
+      <c r="M4" s="51" t="s">
         <v>696</v>
       </c>
-      <c r="M4" s="51" t="s">
+      <c r="N4" s="51" t="s">
         <v>697</v>
       </c>
-      <c r="N4" s="51" t="s">
+      <c r="O4" s="51" t="s">
         <v>698</v>
       </c>
-      <c r="O4" s="51" t="s">
+      <c r="R4" s="51" t="s">
         <v>699</v>
       </c>
-      <c r="R4" s="51" t="s">
+      <c r="S4" s="51" t="s">
         <v>700</v>
-      </c>
-      <c r="S4" s="51" t="s">
-        <v>701</v>
       </c>
       <c r="T4" s="51" t="s">
         <v>75</v>
@@ -26947,10 +26956,10 @@
     </row>
     <row r="5" spans="3:21">
       <c r="C5" s="51" t="s">
+        <v>701</v>
+      </c>
+      <c r="E5" s="51" t="s">
         <v>702</v>
-      </c>
-      <c r="E5" s="51" t="s">
-        <v>703</v>
       </c>
       <c r="F5" s="51">
         <v>2022</v>
@@ -26983,13 +26992,13 @@
         <v>620</v>
       </c>
       <c r="R5" s="51" t="s">
+        <v>703</v>
+      </c>
+      <c r="S5" s="52" t="s">
         <v>704</v>
       </c>
-      <c r="S5" s="52" t="s">
+      <c r="T5" s="51" t="s">
         <v>705</v>
-      </c>
-      <c r="T5" s="51" t="s">
-        <v>706</v>
       </c>
       <c r="U5" s="51" t="s">
         <v>132</v>
@@ -26997,10 +27006,10 @@
     </row>
     <row r="6" spans="3:21">
       <c r="C6" s="51" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E6" s="51" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="F6" s="51">
         <v>2022</v>
@@ -27035,10 +27044,10 @@
     </row>
     <row r="7" spans="3:21">
       <c r="D7" s="51" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="E7" s="51" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="F7" s="51">
         <v>2022</v>
@@ -27073,10 +27082,10 @@
     </row>
     <row r="8" spans="3:21">
       <c r="D8" s="51" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="E8" s="51" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="F8" s="51">
         <v>2022</v>
@@ -27111,10 +27120,10 @@
     </row>
     <row r="9" spans="3:21">
       <c r="D9" s="51" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="E9" s="51" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="F9" s="51">
         <v>2022</v>
@@ -27149,10 +27158,10 @@
     </row>
     <row r="10" spans="3:21">
       <c r="D10" s="51" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="E10" s="51" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="F10" s="51">
         <v>2022</v>
@@ -27187,10 +27196,10 @@
     </row>
     <row r="11" spans="3:21">
       <c r="C11" s="51" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="E11" s="51" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="F11" s="51">
         <v>2022</v>
@@ -27225,10 +27234,10 @@
     </row>
     <row r="12" spans="3:21">
       <c r="C12" s="51" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="E12" s="51" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="F12" s="51">
         <v>2022</v>
@@ -27263,10 +27272,10 @@
     </row>
     <row r="13" spans="3:21">
       <c r="C13" s="51" t="s">
+        <v>701</v>
+      </c>
+      <c r="E13" s="51" t="s">
         <v>702</v>
-      </c>
-      <c r="E13" s="51" t="s">
-        <v>703</v>
       </c>
       <c r="F13" s="51">
         <v>2030</v>
@@ -27301,10 +27310,10 @@
     </row>
     <row r="14" spans="3:21">
       <c r="C14" s="51" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E14" s="51" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="F14" s="51">
         <v>2030</v>
@@ -27339,10 +27348,10 @@
     </row>
     <row r="15" spans="3:21">
       <c r="D15" s="51" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="E15" s="51" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="F15" s="51">
         <v>2030</v>
@@ -27377,10 +27386,10 @@
     </row>
     <row r="16" spans="3:21">
       <c r="D16" s="51" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="E16" s="51" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="F16" s="51">
         <v>2030</v>
@@ -27415,10 +27424,10 @@
     </row>
     <row r="17" spans="3:15">
       <c r="D17" s="51" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="E17" s="51" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="F17" s="51">
         <v>2030</v>
@@ -27453,10 +27462,10 @@
     </row>
     <row r="18" spans="3:15">
       <c r="D18" s="51" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="E18" s="51" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="F18" s="51">
         <v>2030</v>
@@ -27491,10 +27500,10 @@
     </row>
     <row r="19" spans="3:15">
       <c r="C19" s="51" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="E19" s="51" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="F19" s="51">
         <v>2030</v>
@@ -27529,10 +27538,10 @@
     </row>
     <row r="20" spans="3:15">
       <c r="C20" s="51" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="E20" s="51" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="F20" s="51">
         <v>2030</v>
@@ -27567,10 +27576,10 @@
     </row>
     <row r="21" spans="3:15">
       <c r="C21" s="51" t="s">
+        <v>701</v>
+      </c>
+      <c r="E21" s="51" t="s">
         <v>702</v>
-      </c>
-      <c r="E21" s="51" t="s">
-        <v>703</v>
       </c>
       <c r="F21" s="51">
         <v>2050</v>
@@ -27605,10 +27614,10 @@
     </row>
     <row r="22" spans="3:15">
       <c r="C22" s="51" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E22" s="51" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="F22" s="51">
         <v>2050</v>
@@ -27643,10 +27652,10 @@
     </row>
     <row r="23" spans="3:15">
       <c r="D23" s="51" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="E23" s="51" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="F23" s="51">
         <v>2050</v>
@@ -27681,10 +27690,10 @@
     </row>
     <row r="24" spans="3:15">
       <c r="D24" s="51" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="E24" s="51" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="F24" s="51">
         <v>2050</v>
@@ -27719,10 +27728,10 @@
     </row>
     <row r="25" spans="3:15">
       <c r="D25" s="51" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="E25" s="51" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="F25" s="51">
         <v>2050</v>
@@ -27757,10 +27766,10 @@
     </row>
     <row r="26" spans="3:15">
       <c r="D26" s="51" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="E26" s="51" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="F26" s="51">
         <v>2050</v>
@@ -27795,10 +27804,10 @@
     </row>
     <row r="27" spans="3:15">
       <c r="C27" s="51" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="E27" s="51" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="F27" s="51">
         <v>2050</v>
@@ -27833,10 +27842,10 @@
     </row>
     <row r="28" spans="3:15">
       <c r="C28" s="51" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="E28" s="51" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="F28" s="51">
         <v>2050</v>
